--- a/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 6,19</t>
+          <t>-17,64; 7,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 13,42</t>
+          <t>-12,5; 11,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,36; 1,01</t>
+          <t>-24,24; 0,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 7,2</t>
+          <t>-13,02; 7,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,06; 22,93</t>
+          <t>-40,58; 27,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 17,91</t>
+          <t>-14,43; 15,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 0,99</t>
+          <t>-29,41; -0,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,99; 34,71</t>
+          <t>-40,43; 35,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 16,41</t>
+          <t>-7,8; 17,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 5,82</t>
+          <t>-17,47; 5,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 21,21</t>
+          <t>-1,54; 20,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 15,19</t>
+          <t>-7,66; 16,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 61,72</t>
+          <t>-20,68; 69,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 7,02</t>
+          <t>-19,87; 6,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 35,68</t>
+          <t>-2,15; 34,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 62,36</t>
+          <t>-21,67; 69,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 11,44</t>
+          <t>-12,46; 11,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 10,6</t>
+          <t>-9,83; 10,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 18,39</t>
+          <t>-11,98; 17,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 12,88</t>
+          <t>-16,98; 13,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 47,13</t>
+          <t>-37,24; 52,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 13,56</t>
+          <t>-11,07; 12,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 31,08</t>
+          <t>-16,75; 29,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,17; 45,99</t>
+          <t>-40,74; 52,44</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 6,55</t>
+          <t>-11,12; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 2,28</t>
+          <t>-12,09; 2,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 9,51</t>
+          <t>-8,18; 7,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 6,75</t>
+          <t>-14,99; 4,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 24,52</t>
+          <t>-31,92; 19,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 2,7</t>
+          <t>-13,7; 2,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 14,03</t>
+          <t>-11,12; 11,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,82; 25,2</t>
+          <t>-44,22; 17,13</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 15,58</t>
+          <t>-9,73; 15,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 15,96</t>
+          <t>-2,37; 15,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 4,11</t>
+          <t>-17,46; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 2,75</t>
+          <t>-21,08; 3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,01; 55,27</t>
+          <t>-27,51; 56,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 22,11</t>
+          <t>-2,73; 20,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,36; 6,28</t>
+          <t>-22,39; 6,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 8,57</t>
+          <t>-43,43; 9,06</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 21,95</t>
+          <t>-0,4; 22,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 9,02</t>
+          <t>-12,93; 9,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 11,47</t>
+          <t>-17,49; 11,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 6,5</t>
+          <t>-21,9; 5,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 148,83</t>
+          <t>-2,57; 150,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,26; 11,56</t>
+          <t>-14,94; 11,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 21,85</t>
+          <t>-26,26; 22,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 14,95</t>
+          <t>-38,55; 14,44</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 5,81</t>
+          <t>-3,35; 6,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 3,06</t>
+          <t>-4,74; 3,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 3,08</t>
+          <t>-5,95; 3,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 0,99</t>
+          <t>-10,01; 1,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 20,28</t>
+          <t>-10,22; 22,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,78</t>
+          <t>-5,53; 4,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 4,53</t>
+          <t>-8,34; 4,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 3,1</t>
+          <t>-26,76; 3,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 7,52</t>
+          <t>-16,62; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 11,23</t>
+          <t>-10,6; 11,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 0,06</t>
+          <t>-25,04; -0,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 7,35</t>
+          <t>-13,07; 6,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 27,7</t>
+          <t>-39,34; 28,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 15,15</t>
+          <t>-12,48; 15,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,41; -0,51</t>
+          <t>-30,05; -0,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 35,49</t>
+          <t>-39,98; 27,37</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 17,15</t>
+          <t>-10,14; 15,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 5,43</t>
+          <t>-17,73; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 20,63</t>
+          <t>-1,68; 19,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 16,21</t>
+          <t>-7,58; 15,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,68; 69,25</t>
+          <t>-26,35; 61,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 6,74</t>
+          <t>-20,12; 5,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 34,75</t>
+          <t>-2,5; 32,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 69,58</t>
+          <t>-20,23; 62,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 11,94</t>
+          <t>-12,39; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 10,16</t>
+          <t>-11,15; 10,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,98; 17,38</t>
+          <t>-12,3; 17,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 13,97</t>
+          <t>-18,43; 16,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 52,37</t>
+          <t>-36,96; 53,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 12,96</t>
+          <t>-12,47; 12,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 29,61</t>
+          <t>-16,78; 30,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 52,44</t>
+          <t>-42,99; 60,6</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 5,53</t>
+          <t>-9,68; 6,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 2,19</t>
+          <t>-11,33; 2,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 7,8</t>
+          <t>-8,62; 7,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 4,91</t>
+          <t>-15,68; 5,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 19,86</t>
+          <t>-27,24; 26,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 2,53</t>
+          <t>-12,88; 3,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 11,9</t>
+          <t>-11,6; 11,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 17,13</t>
+          <t>-44,13; 21,7</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 15,44</t>
+          <t>-8,44; 15,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 15,46</t>
+          <t>-3,22; 14,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 4,06</t>
+          <t>-17,5; 4,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 3,43</t>
+          <t>-21,69; 2,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 56,36</t>
+          <t>-22,17; 60,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 20,46</t>
+          <t>-3,8; 19,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 6,04</t>
+          <t>-22,43; 6,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 9,06</t>
+          <t>-43,02; 7,77</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 22,29</t>
+          <t>-0,09; 23,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 9,2</t>
+          <t>-13,03; 9,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 11,76</t>
+          <t>-17,06; 10,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 5,79</t>
+          <t>-23,48; 8,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 150,08</t>
+          <t>-3,44; 147,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 11,84</t>
+          <t>-15,13; 12,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 22,88</t>
+          <t>-26,48; 21,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 14,44</t>
+          <t>-41,13; 19,77</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,35</t>
+          <t>-3,05; 5,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 3,39</t>
+          <t>-4,83; 3,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 3,11</t>
+          <t>-6,37; 2,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 1,05</t>
+          <t>-9,66; 1,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 22,95</t>
+          <t>-9,47; 20,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,17</t>
+          <t>-5,6; 4,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 4,57</t>
+          <t>-8,8; 4,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 3,51</t>
+          <t>-25,87; 3,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,16</t>
+          <t>-4,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,62%</t>
+          <t>-16,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 8,06</t>
+          <t>-17,13; 6,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 11,57</t>
+          <t>-10,08; 13,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,04; -0,69</t>
+          <t>-24,36; 1,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 6,47</t>
+          <t>-15,42; 5,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 28,17</t>
+          <t>-41,06; 22,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 15,8</t>
+          <t>-11,77; 17,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,05; -0,96</t>
+          <t>-28,98; 0,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,98; 27,37</t>
+          <t>-44,03; 22,28</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 15,73</t>
+          <t>-9,14; 16,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 4,11</t>
+          <t>-15,93; 5,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 19,6</t>
+          <t>-2,43; 21,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 15,48</t>
+          <t>-7,88; 15,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 61,76</t>
+          <t>-24,14; 61,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 5,05</t>
+          <t>-18,78; 7,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 32,11</t>
+          <t>-2,84; 35,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 62,26</t>
+          <t>-21,86; 62,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,64</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,98%</t>
+          <t>-4,52%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 11,74</t>
+          <t>-12,91; 11,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 10,24</t>
+          <t>-9,79; 10,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 17,35</t>
+          <t>-12,42; 18,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 16,15</t>
+          <t>-17,63; 14,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 53,4</t>
+          <t>-39,76; 47,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 12,82</t>
+          <t>-11,15; 13,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 30,16</t>
+          <t>-17,62; 31,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,99; 60,6</t>
+          <t>-40,88; 49,03</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-2,11</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,5%</t>
+          <t>-6,91%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 6,8</t>
+          <t>-10,97; 6,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 2,56</t>
+          <t>-12,01; 2,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 7,45</t>
+          <t>-8,2; 9,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,68; 5,7</t>
+          <t>-10,21; 6,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 26,16</t>
+          <t>-31,01; 24,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 3,06</t>
+          <t>-13,35; 2,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 11,28</t>
+          <t>-10,89; 14,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 21,7</t>
+          <t>-29,81; 27,89</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>-6,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-18,7%</t>
+          <t>-15,93%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 15,84</t>
+          <t>-9,11; 15,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 14,9</t>
+          <t>-2,55; 15,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,5; 4,0</t>
+          <t>-17,14; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 2,64</t>
+          <t>-19,42; 3,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 60,48</t>
+          <t>-25,01; 55,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 19,75</t>
+          <t>-2,72; 22,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 6,06</t>
+          <t>-22,36; 6,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 7,77</t>
+          <t>-38,42; 11,17</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-7,67</t>
+          <t>-11,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-15,64%</t>
+          <t>-22,82%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 23,19</t>
+          <t>-0,03; 21,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 9,75</t>
+          <t>-13,92; 9,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 10,89</t>
+          <t>-17,99; 11,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,48; 8,11</t>
+          <t>-29,1; 2,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 147,48</t>
+          <t>-2,01; 148,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 12,67</t>
+          <t>-16,26; 11,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 21,42</t>
+          <t>-27,45; 21,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 19,77</t>
+          <t>-47,81; 5,63</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,82</t>
+          <t>-3,54</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-11,08%</t>
+          <t>-9,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 5,87</t>
+          <t>-3,5; 5,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,3</t>
+          <t>-4,73; 3,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,72</t>
+          <t>-5,99; 3,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 1,25</t>
+          <t>-8,85; 0,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 20,44</t>
+          <t>-10,91; 20,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,06</t>
+          <t>-5,55; 3,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 4,04</t>
+          <t>-8,3; 4,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 3,76</t>
+          <t>-23,06; 2,97</t>
         </is>
       </c>
     </row>
